--- a/MainTop/03.08.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/03.08.2026 Макс Озон/print_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\03.08.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BA3137-3875-4BFF-9E17-54525ECED888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A1CE21-AAC9-48F5-BC05-98C42DC90131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 

--- a/MainTop/03.08.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/03.08.2026 Макс Озон/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\03.08.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A1CE21-AAC9-48F5-BC05-98C42DC90131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FC8FBC-FBE5-42D9-9838-E670F1511DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
